--- a/Figure 6/Figure 6-J.xlsx
+++ b/Figure 6/Figure 6-J.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics7798648\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1D723A-757F-4D8B-9A26-4A29F693FA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C1FB81-B58A-48AA-8F3A-745C4DCAD4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27490" yWindow="4780" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-1540" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>IL-6(ng/L)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,10 +60,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ETEC 6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CON 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,10 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ETEC+WB800 6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ETEC+WB800_KR32 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -129,10 +121,6 @@
   </si>
   <si>
     <t>ETEC+WB800_KR32 5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ETEC+WB800_KR32 6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -160,10 +148,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -188,7 +175,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -470,201 +457,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1003.646468664179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1">
-        <v>1003.646468664179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" s="2">
+        <v>904.51127425485606</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1">
-        <v>904.51127425485606</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" s="2">
+        <v>939.00488984385345</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1">
-        <v>939.00488984385345</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" s="2">
+        <v>907.49891025075362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1">
-        <v>907.49891025075362</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" s="2">
+        <v>833.6228201703816</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1">
-        <v>833.6228201703816</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" s="2">
+        <v>997.1279901276755</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1182.6330251456686</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1006.0908981153677</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1008.5353275665564</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1150.8554422802144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1244.8301745148053</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1">
-        <v>997.1279901276755</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="1">
+      <c r="B13" s="2">
+        <v>1240.7561254294908</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1143.7937571990024</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1039.4981006149478</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1162.2627797190955</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1147.0529964672542</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
         <v>889.5567856595577</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
         <v>990.05456038662828</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
         <v>978.26020051645867</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
         <v>993.00315035417077</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="1">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
         <v>894.96253393338532</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1182.6330251456686</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1006.0908981153677</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1008.5353275665564</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1150.8554422802144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1">
-        <v>1244.8301745148053</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1240.7561254294908</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1143.7937571990024</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1039.4981006149478</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1162.2627797190955</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1">
-        <v>1147.0529964672542</v>
       </c>
     </row>
   </sheetData>
